--- a/cases/lebron-vs-michael/published/LeBron Vs. Michael - Data.xlsx
+++ b/cases/lebron-vs-michael/published/LeBron Vs. Michael - Data.xlsx
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -743,6 +743,11 @@
           <t>Rebounds</t>
         </is>
       </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Blocks</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -780,6 +785,9 @@
       <c r="K5" s="6" t="n">
         <v>9751</v>
       </c>
+      <c r="L5" s="6" t="n">
+        <v>982</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -816,6 +824,9 @@
       </c>
       <c r="K6" s="10" t="n">
         <v>6672</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>893</v>
       </c>
     </row>
   </sheetData>
@@ -830,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -916,6 +927,11 @@
           <t>Rebounds</t>
         </is>
       </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Blocks</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -953,6 +969,9 @@
       <c r="K6" s="10" t="n">
         <v>2392</v>
       </c>
+      <c r="L6" s="10" t="n">
+        <v>253</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -989,6 +1008,9 @@
       </c>
       <c r="K7" s="6" t="n">
         <v>1151</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
